--- a/food_beverage_order_forms/042_food_safety_inspection_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/042_food_safety_inspection_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'d'}</t>
+          <t>d</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'D'}</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'risk_1'}</t>
+          <t>risk_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Risk 1'}</t>
+          <t>Risk 1</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'risk_2'}</t>
+          <t>risk_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Risk 2'}</t>
+          <t>Risk 2</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'risk_3'}</t>
+          <t>risk_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Risk 3'}</t>
+          <t>Risk 3</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'action_1'}</t>
+          <t>action_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Action 1'}</t>
+          <t>Action 1</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'action_2'}</t>
+          <t>action_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Action 2'}</t>
+          <t>Action 2</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'action_3'}</t>
+          <t>action_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Action 3'}</t>
+          <t>Action 3</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'action_1'}</t>
+          <t>action_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Action 1'}</t>
+          <t>Action 1</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'action_2'}</t>
+          <t>action_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Action 2'}</t>
+          <t>Action 2</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'action_3'}</t>
+          <t>action_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Action 3'}</t>
+          <t>Action 3</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'action_1'}</t>
+          <t>action_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Action 1'}</t>
+          <t>Action 1</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'action_2'}</t>
+          <t>action_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Action 2'}</t>
+          <t>Action 2</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'action_3'}</t>
+          <t>action_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Action 3'}</t>
+          <t>Action 3</t>
         </is>
       </c>
     </row>
